--- a/scripts/master-node-table.xlsx
+++ b/scripts/master-node-table.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +80,19 @@
       <b val="1"/>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +149,26 @@
         <fgColor rgb="00059669"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -165,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -252,6 +283,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -634,12 +686,13 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SwipeEd — Master Node Table  (drop-in path spec: 36 games + 5 capstones, in order)</t>
+          <t>SwipeEd — Master Node Table  (drop-in path spec: 39 games + 5 capstones, in order)</t>
         </is>
       </c>
     </row>
@@ -707,6 +760,11 @@
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>gating</t>
         </is>
       </c>
     </row>
@@ -754,7 +812,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>5.2, 5.3 (emotions)</t>
+          <t>5.2, 5.3, 5.6 (emotions)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -770,6 +828,11 @@
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Name emotions &amp; say 'no' — the base for everything</t>
+        </is>
+      </c>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -835,6 +898,11 @@
           <t>Your body is yours; safe vs unsafe touch</t>
         </is>
       </c>
+      <c r="N4" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -842,12 +910,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>g03</t>
+          <t>g37</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>My Family Garden</t>
+          <t>Clean Crew</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -863,24 +931,24 @@
       <c r="F5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Body &amp; Growing Up</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#0EA5E9</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 7.1</t>
+          <t>6.5, 6.1</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -895,7 +963,12 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Families &amp; friends; kinds of love</t>
+          <t>Caring for your body: washing, brushing &amp; healthy habits</t>
+        </is>
+      </c>
+      <c r="N5" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -905,12 +978,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>g04</t>
+          <t>g03</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Same Same, Different</t>
+          <t>My Family Garden</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -926,29 +999,29 @@
       <c r="F6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>3.1, 1.3</t>
+          <t>1.1, 1.2, 7.1</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>g03</t>
+          <t>g37</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -958,7 +1031,12 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>We're equal inside; difference is wonderful</t>
+          <t>Families &amp; friends; kinds of love</t>
+        </is>
+      </c>
+      <c r="N6" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -968,12 +1046,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>g05</t>
+          <t>g04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Can-Do Kids</t>
+          <t>Same Same, Different</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1006,148 +1084,163 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
+          <t>3.1, 1.3</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>g03</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>We're equal inside; difference is wonderful</t>
+        </is>
+      </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>g05</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Can-Do Kids</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Ch.1 · Ages 3–6</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>g04</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>g04</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Anyone can do anything, whatever their gender</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>c1</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Capstone: My First Friends</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Ch.1 · Ages 3–6</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>g05</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>Chapter 1 graduation — the Friendship Garden blooms</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>g06</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Body Lab Juniors</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Ch.2 · Ages 6–9</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Body &amp; Growing Up</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>#0EA5E9</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>6.1, 6.2, 6.3, 6.4</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>c1</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>g02</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>How bodies work &amp; grow</t>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1250,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>g07</t>
+          <t>g06</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>What Makes Me, Me</t>
+          <t>Body Lab Juniors</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1178,39 +1271,44 @@
       <c r="F10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Body &amp; Growing Up</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#0EA5E9</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.1, 6.2, 6.3, 6.4, 6.5</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>g06</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>g04</t>
+          <t>g02</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Sex vs gender — base of the gender thread</t>
+          <t>How bodies work &amp; grow</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1318,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>g08</t>
+          <t>g07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Safety Squad</t>
+          <t>What Makes Me, Me</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1241,39 +1339,44 @@
       <c r="F11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>4.1, 4.2, 4.3, 3.3, 5.5</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>g07</t>
+          <t>g06</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>g02</t>
+          <t>g04</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Touch, privacy &amp; online safety</t>
+          <t>Sex vs gender — base of the gender thread</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1386,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>g09</t>
+          <t>g08</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Friend or Frenemy?</t>
+          <t>Safety Squad</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1304,39 +1407,44 @@
       <c r="F12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>1.2, 5.1, 5.3, 7.1</t>
+          <t>4.1, 4.2, 4.3, 3.3, 5.5</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>g08</t>
+          <t>g07</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>g03</t>
+          <t>g02</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Healthy vs unhealthy friendships</t>
+          <t>Touch, privacy &amp; online safety</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1454,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g09</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Fair Play World</t>
+          <t>Friend or Frenemy?</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1367,39 +1475,44 @@
       <c r="F13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>3.2, 1.1, 1.3, 1.4, 2.1, 2.2, 2.3</t>
+          <t>1.2, 5.1, 5.3, 5.6, 7.1</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>g09</t>
+          <t>g08</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>g07</t>
+          <t>g03</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Sharing chores &amp; opportunity fairly</t>
+          <t>Healthy vs unhealthy friendships</t>
+        </is>
+      </c>
+      <c r="N13" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1522,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>g11</t>
+          <t>g10</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Not Fair, Not Funny</t>
+          <t>Fair Play World</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1447,22 +1560,27 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2, 1.1, 1.3, 1.4, 2.1, 2.2, 2.3</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g09</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g07</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Gender teasing, and being an ally</t>
+          <t>Sharing chores &amp; opportunity fairly</t>
+        </is>
+      </c>
+      <c r="N14" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1590,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>g12</t>
+          <t>g11</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Smart Screen Heroes</t>
+          <t>Not Fair, Not Funny</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1493,165 +1611,180 @@
       <c r="F15" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Gender teasing, and being an ally</t>
+        </is>
+      </c>
+      <c r="N15" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Smart Screen Heroes</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Ch.2 · Ages 6–9</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>5.2, 5.4, 8.2, 8.3</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>g11</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Media real-vs-pretend, choices, hygiene, caring</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="N16" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>c2</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Capstone: Fair &amp; Safe Explorer</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Ch.2 · Ages 6–9</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F17" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>g12</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" s="13" t="inlineStr">
+      <c r="M17" s="13" t="inlineStr">
         <is>
           <t>Chapter 2 graduation</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>g13</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Puberty Quest</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Ch.3 · Ages 9–12</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Body &amp; Growing Up</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>#0EA5E9</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>6.3, 6.1, 6.4, 7.2</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>g06</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Puberty — timely; builds on Body Lab</t>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1794,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>g14</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>The Amazing Journey</t>
+          <t>Puberty Quest</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1682,39 +1815,44 @@
       <c r="F18" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Body &amp; Growing Up</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#0EA5E9</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>6.2, 8.1</t>
+          <t>6.3, 6.1, 6.4, 6.5, 7.2</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>g13</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>g13</t>
+          <t>g06</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Reproduction — after anatomy &amp; puberty</t>
+          <t>Puberty — timely; builds on Body Lab</t>
+        </is>
+      </c>
+      <c r="N18" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1862,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g38</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Boundary Bot</t>
+          <t>Mind Matters</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1745,39 +1883,44 @@
       <c r="F19" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Feelings &amp; Life Skills</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#F59E0B</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>4.1, 4.2, 4.3, 3.3, 5.5</t>
+          <t>5.6, 5.5</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>g14</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>g08</t>
+          <t>g01</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Consent, boundaries &amp; online safety</t>
+          <t>Big feelings, stress &amp; rejection; bouncing back &amp; asking for help</t>
+        </is>
+      </c>
+      <c r="N19" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1930,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>g16</t>
+          <t>g14</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>The Amazing Journey</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1808,39 +1951,44 @@
       <c r="F20" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.4, 5.1, 5.2, 5.3, 7.1</t>
+          <t>6.2, 8.1</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g38</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>g09</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Peer pressure, decisions &amp; feelings</t>
+          <t>Reproduction — after anatomy &amp; puberty</t>
+        </is>
+      </c>
+      <c r="N20" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1998,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>g17</t>
+          <t>g15</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Flip the Script</t>
+          <t>Boundary Bot</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1871,39 +2019,44 @@
       <c r="F21" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>3.1, 3.2, 1.3, 2.1, 2.2, 2.3, 5.4</t>
+          <t>4.1, 4.2, 4.3, 3.3, 5.5</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>g16</t>
+          <t>g14</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g08</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Spot &amp; remix gender stereotypes in media</t>
+          <t>Consent, boundaries &amp; online safety</t>
+        </is>
+      </c>
+      <c r="N21" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1913,12 +2066,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>g18</t>
+          <t>g16</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Norm Storm</t>
+          <t>Crossroads</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1934,39 +2087,44 @@
       <c r="F22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>3.2, 2.3</t>
+          <t>1.1, 1.2, 1.4, 5.1, 5.2, 5.3, 7.1</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>g17</t>
+          <t>g15</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>g17</t>
+          <t>g09</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Which social norms help, and which harm</t>
+          <t>Peer pressure, decisions &amp; feelings</t>
+        </is>
+      </c>
+      <c r="N22" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1976,12 +2134,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>g19</t>
+          <t>g17</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Speak Up</t>
+          <t>Flip the Script</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2014,22 +2172,27 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>3.3, 5.5</t>
+          <t>3.1, 3.2, 1.3, 2.1, 2.2, 2.3, 5.4</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>g18</t>
+          <t>g16</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>g11</t>
+          <t>g10</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Forms of gender-based harm &amp; where to get help</t>
+          <t>Spot &amp; remix gender stereotypes in media</t>
+        </is>
+      </c>
+      <c r="N23" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2202,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>g20</t>
+          <t>g18</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Defenders of the Body</t>
+          <t>Norm Storm</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2060,102 +2223,112 @@
       <c r="F24" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>3.2, 2.3</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
+          <t>g17</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>g17</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Which social norms help, and which harm</t>
+        </is>
+      </c>
+      <c r="N24" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>g19</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>g12</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>HIV &amp; infections; reducing stigma</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>c3</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Capstone: Growing Up Smart</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Capstone</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Speak Up</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Ch.3 · Ages 9–12</t>
         </is>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>Capstone milestone</t>
-        </is>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>#EAB308</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>g20</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 3 graduation</t>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>3.3, 5.5</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>g18</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>g11</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Forms of gender-based harm &amp; where to get help</t>
+        </is>
+      </c>
+      <c r="N25" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2338,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>g21</t>
+          <t>g20</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Body Confident</t>
+          <t>Defenders of the Body</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2180,108 +2353,118 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Ch.4 · Ages 12–15</t>
+          <t>Ch.3 · Ages 9–12</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>9</v>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Body &amp; Growing Up</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>#0EA5E9</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>6.1, 6.3, 6.4</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
+          <t>g19</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>HIV &amp; infections; reducing stigma</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
           <t>c3</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>g13</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Puberty depth &amp; body image</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>g22</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Plan It</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Ch.4 · Ages 12–15</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Sexual &amp; Reproductive Health</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>#059669</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>6.2, 8.1</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>g21</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>g14</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Fertility, pregnancy &amp; contraception</t>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Capstone: Growing Up Smart</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Capstone</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Ch.3 · Ages 9–12</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Capstone milestone</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>#EAB308</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>g20</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 3 graduation</t>
+        </is>
+      </c>
+      <c r="N27" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2474,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g21</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Outbreak: Stop the Spread</t>
+          <t>Body Confident</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2312,39 +2495,44 @@
       <c r="F28" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Body &amp; Growing Up</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#0EA5E9</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>6.1, 6.3, 6.4</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>g22</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>g20</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>STIs &amp; HIV</t>
+          <t>Puberty depth &amp; body image</t>
+        </is>
+      </c>
+      <c r="N28" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2542,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g39</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Green Light / Red Light</t>
+          <t>Bounce</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -2375,39 +2563,44 @@
       <c r="F29" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Feelings &amp; Life Skills</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#F59E0B</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>1.2, 4.2, 5.3, 7.1, 7.2</t>
+          <t>5.6, 5.5</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g21</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g38</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Reading healthy vs unhealthy relationships (flagship)</t>
+          <t>Resilience, stress &amp; mental health; supporting friends</t>
+        </is>
+      </c>
+      <c r="N29" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2610,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>g25</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>MythBuster: Gender</t>
+          <t>Plan It</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2438,39 +2631,44 @@
       <c r="F30" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>3.1, 3.2</t>
+          <t>6.2, 8.1</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g39</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>g18</t>
+          <t>g14</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Bust the gender myths teens hear constantly</t>
+          <t>Fertility, pregnancy &amp; contraception</t>
+        </is>
+      </c>
+      <c r="N30" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2678,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Equalize</t>
+          <t>Outbreak: Stop the Spread</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2501,39 +2699,44 @@
       <c r="F31" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>3.1, 3.2, 1.4, 2.2, 3.3, 4.1</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>g25</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g20</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Equality pays off; child marriage</t>
+          <t>STIs &amp; HIV</t>
+        </is>
+      </c>
+      <c r="N31" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2746,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Stand Up</t>
+          <t>Green Light / Red Light</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2581,22 +2784,27 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>3.3, 4.1, 2.2</t>
+          <t>1.2, 4.2, 5.3, 7.1, 7.2</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>g19</t>
+          <t>g15</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>GBV: bystander action &amp; rights</t>
+          <t>Reading healthy vs unhealthy relationships (flagship)</t>
+        </is>
+      </c>
+      <c r="N32" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2814,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>g28</t>
+          <t>g25</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Reality Check</t>
+          <t>MythBuster: Gender</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2627,102 +2835,112 @@
       <c r="F33" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Values, Rights &amp; Media</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>#475569</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>5.1, 5.2, 5.4, 5.5, 2.1, 2.3</t>
+          <t>3.1, 3.2</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>g16</t>
+          <t>g18</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Decisions, media &amp; pornography literacy, finding help</t>
+          <t>Bust the gender myths teens hear constantly</t>
+        </is>
+      </c>
+      <c r="N33" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>c4</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Capstone: Reading Relationships</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Capstone</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>g26</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Equalize</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Ch.4 · Ages 12–15</t>
         </is>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>Capstone milestone</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>#EAB308</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="11" t="inlineStr">
-        <is>
-          <t>g28</t>
-        </is>
-      </c>
-      <c r="L34" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 4 graduation</t>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>3.1, 3.2, 1.4, 2.2, 3.3, 4.1</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>g25</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Equality pays off; child marriage</t>
+        </is>
+      </c>
+      <c r="N34" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2950,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>g29</t>
+          <t>g27</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>My Choices, My Future</t>
+          <t>Stand Up</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2747,45 +2965,50 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Ch.5 · Ages 15–18</t>
+          <t>Ch.4 · Ages 12–15</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>12</v>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
+          <t>3.3, 4.1, 2.2</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>g26</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>g22</t>
+          <t>g19</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Contraception, family planning &amp; services</t>
+          <t>GBV: bystander action &amp; rights</t>
+        </is>
+      </c>
+      <c r="N35" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2795,12 +3018,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g28</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Status: Know It</t>
+          <t>Reality Check</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -2810,108 +3033,118 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Ch.5 · Ages 15–18</t>
+          <t>Ch.4 · Ages 12–15</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>12</v>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Values, Rights &amp; Media</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#475569</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>5.1, 5.2, 5.4, 5.5, 2.1, 2.3</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>g29</t>
+          <t>g27</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g16</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>STI/HIV testing &amp; treatment</t>
+          <t>Decisions, media &amp; pornography literacy, finding help</t>
+        </is>
+      </c>
+      <c r="N36" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>g31</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Mutual</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Ch.5 · Ages 15–18</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Safety, Consent &amp; Boundaries</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>#DC2626</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>g30</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>g24</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Sexual consent, legal age &amp; relationships</t>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Capstone: Reading Relationships</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Capstone</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Ch.4 · Ages 12–15</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Capstone milestone</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>#EAB308</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>g28</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4 graduation</t>
+        </is>
+      </c>
+      <c r="N37" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2921,12 +3154,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Spectrum</t>
+          <t>My Choices, My Future</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2942,39 +3175,44 @@
       <c r="F38" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>7.1, 1.3, 3.1</t>
+          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Identity, orientation &amp; respect</t>
+          <t>Contraception, family planning &amp; services</t>
+        </is>
+      </c>
+      <c r="N38" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -2984,12 +3222,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Lead the Way</t>
+          <t>Status: Know It</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3005,39 +3243,44 @@
       <c r="F39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Structural equality: pay gap, leadership, unpaid care</t>
+          <t>STI/HIV testing &amp; treatment</t>
+        </is>
+      </c>
+      <c r="N39" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3290,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Change Makers</t>
+          <t>Mutual</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3068,39 +3311,44 @@
       <c r="F40" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
+          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Campaign vs GBV &amp; inequality; the law</t>
+          <t>Sexual consent, legal age &amp; relationships</t>
+        </is>
+      </c>
+      <c r="N40" s="34" t="inlineStr">
+        <is>
+          <t>Sensitive ⚑</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3358,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>g35</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Justice League: Rights Edition</t>
+          <t>Spectrum</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3131,39 +3379,44 @@
       <c r="F41" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Values, Rights &amp; Media</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>#475569</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+          <t>7.1, 1.3, 3.1</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Rights &amp; redress pathways</t>
+          <t>Identity, orientation &amp; respect</t>
+        </is>
+      </c>
+      <c r="N41" s="34" t="inlineStr">
+        <is>
+          <t>Sensitive ⚑</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3426,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>g36</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Decoded</t>
+          <t>Lead the Way</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3194,108 +3447,322 @@
       <c r="F42" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>g32</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>g26</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Structural equality: pay gap, leadership, unpaid care</t>
+        </is>
+      </c>
+      <c r="N42" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>g34</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Change Makers</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>g33</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>g26</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Campaign vs GBV &amp; inequality; the law</t>
+        </is>
+      </c>
+      <c r="N43" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>g35</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Justice League: Rights Edition</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>5.4, 4.3, 5.1, 2.1, 2.3, 1.1</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>g34</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>g27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Rights &amp; redress pathways</t>
+        </is>
+      </c>
+      <c r="N44" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>g36</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Decoded</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Values, Rights &amp; Media</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>#475569</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>5.4, 4.3, 5.1, 5.6, 2.1, 2.3, 1.1</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>g35</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Pornography &amp; critical thinking online</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="N45" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>c5</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Capstone: Ready for the World</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Ch.5 · Ages 15–18</t>
         </is>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F46" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I43" s="15" t="inlineStr">
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>g36</t>
         </is>
       </c>
-      <c r="L43" s="11" t="inlineStr">
+      <c r="L46" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M43" s="13" t="inlineStr">
+      <c r="M46" s="13" t="inlineStr">
         <is>
           <t>Final graduation — look back at the whole world built since age 4</t>
+        </is>
+      </c>
+      <c r="N46" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3307,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3594,6 +4061,50 @@
       <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Column names are field-ready: { order, id, label, type, chapter, ageGate, thread, hex, topics[], prereq, buildsOn, note }.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>gating (new column)</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>School-comfort level — Core / Gated / Sensitive ⚑ (flaggable). Mirrors the Topic Map; gate via school-comfort toggle or remove sensitive nodes per context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>node_id vs order</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>node_id (g01–g39, c1–c5) is a STABLE id — GDD filenames track it. The "order" column is the true play sequence; new games keep their id but sit earlier in order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="inlineStr">
+        <is>
+          <t>Update — June 2026</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>Added 3 nodes to fill map gaps:</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>g37 Clean Crew (hygiene/self-care, Ch.1) · g38 Mind Matters (mental wellbeing, Ch.3) · g39 Bounce (resilience, Ch.4). Now 39 games + 5 capstones = 44 nodes. Topics 5.6/6.5 also mapped onto g01, g06, g09, g13, g36.</t>
         </is>
       </c>
     </row>

--- a/scripts/master-node-table.xlsx
+++ b/scripts/master-node-table.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -305,6 +305,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -670,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -692,7 +693,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SwipeEd — Master Node Table  (drop-in path spec: 39 games + 5 capstones, in order)</t>
+          <t>SwipeEd — Master Node Table  (drop-in path spec: 40 games + 5 capstones, in order)</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3019,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>g28</t>
+          <t>g40</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Reality Check</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3039,180 +3040,180 @@
       <c r="F36" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Safety, Consent &amp; Boundaries</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>#DC2626</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>4.3, 4.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>g27</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>g15</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Teen online safety: grooming, sexting, sextortion &amp; footprint</t>
+        </is>
+      </c>
+      <c r="N36" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>g28</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Reality Check</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Ch.4 · Ages 12–15</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>5.1, 5.2, 5.4, 5.5, 2.1, 2.3</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>g27</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>5.1, 5.2, 5.4, 4.3, 5.5, 2.1, 2.3</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>g40</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>g16</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>Decisions, media &amp; pornography literacy, finding help</t>
         </is>
       </c>
-      <c r="N36" s="33" t="inlineStr">
+      <c r="N37" s="33" t="inlineStr">
         <is>
           <t>Gated</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>c4</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Capstone: Reading Relationships</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Ch.4 · Ages 12–15</t>
         </is>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F38" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="L37" s="11" t="inlineStr">
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M37" s="13" t="inlineStr">
+      <c r="M38" s="13" t="inlineStr">
         <is>
           <t>Chapter 4 graduation</t>
         </is>
       </c>
-      <c r="N37" s="32" t="inlineStr">
+      <c r="N38" s="32" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>g29</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>My Choices, My Future</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Ch.5 · Ages 15–18</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>Sexual &amp; Reproductive Health</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>#059669</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>c4</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>g22</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Contraception, family planning &amp; services</t>
-        </is>
-      </c>
-      <c r="N38" s="33" t="inlineStr">
-        <is>
-          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3223,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Status: Know It</t>
+          <t>My Choices, My Future</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3260,22 +3261,22 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>g29</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>STI/HIV testing &amp; treatment</t>
+          <t>Contraception, family planning &amp; services</t>
         </is>
       </c>
       <c r="N39" s="33" t="inlineStr">
@@ -3290,12 +3291,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Mutual</t>
+          <t>Status: Know It</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3311,44 +3312,44 @@
       <c r="F40" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Sexual consent, legal age &amp; relationships</t>
-        </is>
-      </c>
-      <c r="N40" s="34" t="inlineStr">
-        <is>
-          <t>Sensitive ⚑</t>
+          <t>STI/HIV testing &amp; treatment</t>
+        </is>
+      </c>
+      <c r="N40" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3359,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Spectrum</t>
+          <t>Mutual</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3379,29 +3380,29 @@
       <c r="F41" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>7.1, 1.3, 3.1</t>
+          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -3411,7 +3412,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Identity, orientation &amp; respect</t>
+          <t>Sexual consent, legal age &amp; relationships</t>
         </is>
       </c>
       <c r="N41" s="34" t="inlineStr">
@@ -3426,12 +3427,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Lead the Way</t>
+          <t>Spectrum</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3447,44 +3448,44 @@
       <c r="F42" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>7.1, 1.3, 3.1</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Structural equality: pay gap, leadership, unpaid care</t>
-        </is>
-      </c>
-      <c r="N42" s="31" t="inlineStr">
-        <is>
-          <t>Core</t>
+          <t>Identity, orientation &amp; respect</t>
+        </is>
+      </c>
+      <c r="N42" s="34" t="inlineStr">
+        <is>
+          <t>Sensitive ⚑</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3495,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Change Makers</t>
+          <t>Lead the Way</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3532,12 +3533,12 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -3547,7 +3548,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Campaign vs GBV &amp; inequality; the law</t>
+          <t>Structural equality: pay gap, leadership, unpaid care</t>
         </is>
       </c>
       <c r="N43" s="31" t="inlineStr">
@@ -3562,12 +3563,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>g35</t>
+          <t>g34</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Justice League: Rights Edition</t>
+          <t>Change Makers</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3583,39 +3584,39 @@
       <c r="F44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Values, Rights &amp; Media</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>#475569</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g26</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Rights &amp; redress pathways</t>
+          <t>Campaign vs GBV &amp; inequality; the law</t>
         </is>
       </c>
       <c r="N44" s="31" t="inlineStr">
@@ -3630,12 +3631,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>g36</t>
+          <t>g35</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Decoded</t>
+          <t>Justice League: Rights Edition</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3668,93 +3669,161 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
+          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>g34</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>g27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Rights &amp; redress pathways</t>
+        </is>
+      </c>
+      <c r="N45" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>g36</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Decoded</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Values, Rights &amp; Media</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>#475569</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
           <t>5.4, 4.3, 5.1, 5.6, 2.1, 2.3, 1.1</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>g35</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>Pornography &amp; critical thinking online</t>
         </is>
       </c>
-      <c r="N45" s="33" t="inlineStr">
+      <c r="N46" s="33" t="inlineStr">
         <is>
           <t>Gated</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>c5</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Capstone: Ready for the World</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>Ch.5 · Ages 15–18</t>
         </is>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F47" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr">
+      <c r="I47" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J46" s="13" t="inlineStr">
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>g36</t>
         </is>
       </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="L47" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M46" s="13" t="inlineStr">
+      <c r="M47" s="13" t="inlineStr">
         <is>
           <t>Final graduation — look back at the whole world built since age 4</t>
         </is>
       </c>
-      <c r="N46" s="32" t="inlineStr">
+      <c r="N47" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3774,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4105,6 +4174,20 @@
       <c r="B28" s="36" t="inlineStr">
         <is>
           <t>g37 Clean Crew (hygiene/self-care, Ch.1) · g38 Mind Matters (mental wellbeing, Ch.3) · g39 Bounce (resilience, Ch.4). Now 39 games + 5 capstones = 44 nodes. Topics 5.6/6.5 also mapped onto g01, g06, g09, g13, g36.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>Update — June 2026 (online-safety)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>Added g40 Firewall (teen online safety: grooming/sexting/sextortion/footprint, Ch.4, Thread B, topic 4.3) to close the 12–15 online-safety gap; re-tagged g28 Reality Check with 4.3 (image-abuse/reporting it already covers). Now 40 games + 5 capstones = 45 nodes.</t>
         </is>
       </c>
     </row>

--- a/scripts/master-node-table.xlsx
+++ b/scripts/master-node-table.xlsx
@@ -671,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SwipeEd — Master Node Table  (drop-in path spec: 40 games + 5 capstones, in order)</t>
+          <t>SwipeEd — Master Node Table  (drop-in path spec: 42 games + 5 capstones, in order)</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g41</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Fair Play World</t>
+          <t>Heart Smart</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1544,24 +1544,24 @@
       <c r="F14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Feelings &amp; Life Skills</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#F59E0B</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>3.2, 1.1, 1.3, 1.4, 2.1, 2.2, 2.3</t>
+          <t>5.6, 5.3, 5.2, 1.3</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>g07</t>
+          <t>g01</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Sharing chores &amp; opportunity fairly</t>
+          <t>Empathy, handling feelings &amp; getting along</t>
         </is>
       </c>
       <c r="N14" s="31" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>g11</t>
+          <t>g10</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Not Fair, Not Funny</t>
+          <t>Fair Play World</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1629,22 +1629,22 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2, 1.1, 1.3, 1.4, 2.1, 2.2, 2.3</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g41</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g07</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Gender teasing, and being an ally</t>
+          <t>Sharing chores &amp; opportunity fairly</t>
         </is>
       </c>
       <c r="N15" s="31" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>g12</t>
+          <t>g11</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Smart Screen Heroes</t>
+          <t>Not Fair, Not Funny</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1680,180 +1680,180 @@
       <c r="F16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Gender teasing, and being an ally</t>
+        </is>
+      </c>
+      <c r="N16" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Smart Screen Heroes</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Ch.2 · Ages 6–9</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>5.2, 5.4, 8.2, 8.3</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>g11</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Media real-vs-pretend, choices, hygiene, caring</t>
         </is>
       </c>
-      <c r="N16" s="31" t="inlineStr">
+      <c r="N17" s="31" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>c2</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Capstone: Fair &amp; Safe Explorer</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Ch.2 · Ages 6–9</t>
         </is>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F18" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>g12</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>Chapter 2 graduation</t>
         </is>
       </c>
-      <c r="N17" s="32" t="inlineStr">
+      <c r="N18" s="32" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>g13</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Puberty Quest</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Ch.3 · Ages 9–12</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Body &amp; Growing Up</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>#0EA5E9</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>6.3, 6.1, 6.4, 6.5, 7.2</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>g06</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Puberty — timely; builds on Body Lab</t>
-        </is>
-      </c>
-      <c r="N18" s="31" t="inlineStr">
-        <is>
-          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>g38</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Mind Matters</t>
+          <t>Puberty Quest</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1884,39 +1884,39 @@
       <c r="F19" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Feelings &amp; Life Skills</t>
+          <t>Body &amp; Growing Up</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>#F59E0B</t>
+          <t>#0EA5E9</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>5.6, 5.5</t>
+          <t>6.3, 6.1, 6.4, 6.5, 7.2</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>g13</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>g01</t>
+          <t>g06</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Big feelings, stress &amp; rejection; bouncing back &amp; asking for help</t>
+          <t>Puberty — timely; builds on Body Lab</t>
         </is>
       </c>
       <c r="N19" s="31" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>g14</t>
+          <t>g38</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>The Amazing Journey</t>
+          <t>Mind Matters</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1952,39 +1952,39 @@
       <c r="F20" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Feelings &amp; Life Skills</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#F59E0B</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>6.2, 8.1</t>
+          <t>5.6, 5.5</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>g38</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>g13</t>
+          <t>g01</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Reproduction — after anatomy &amp; puberty</t>
+          <t>Big feelings, stress &amp; rejection; bouncing back &amp; asking for help</t>
         </is>
       </c>
       <c r="N20" s="31" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g14</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Boundary Bot</t>
+          <t>The Amazing Journey</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2020,39 +2020,39 @@
       <c r="F21" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>4.1, 4.2, 4.3, 3.3, 5.5</t>
+          <t>6.2, 8.1</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>g14</t>
+          <t>g38</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>g08</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Consent, boundaries &amp; online safety</t>
+          <t>Reproduction — after anatomy &amp; puberty</t>
         </is>
       </c>
       <c r="N21" s="31" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>g16</t>
+          <t>g15</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>Boundary Bot</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2088,39 +2088,39 @@
       <c r="F22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.4, 5.1, 5.2, 5.3, 7.1</t>
+          <t>4.1, 4.2, 4.3, 3.3, 5.5</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g14</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>g09</t>
+          <t>g08</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Peer pressure, decisions &amp; feelings</t>
+          <t>Consent, boundaries &amp; online safety</t>
         </is>
       </c>
       <c r="N22" s="31" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>g17</t>
+          <t>g16</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Flip the Script</t>
+          <t>Crossroads</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2156,39 +2156,39 @@
       <c r="F23" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>3.1, 3.2, 1.3, 2.1, 2.2, 2.3, 5.4</t>
+          <t>1.1, 1.2, 1.4, 5.1, 5.2, 5.3, 7.1</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>g16</t>
+          <t>g15</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g09</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Spot &amp; remix gender stereotypes in media</t>
+          <t>Peer pressure, decisions &amp; feelings</t>
         </is>
       </c>
       <c r="N23" s="31" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>g18</t>
+          <t>g17</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Norm Storm</t>
+          <t>Flip the Script</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2241,22 +2241,22 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>3.2, 2.3</t>
+          <t>3.1, 3.2, 1.3, 2.1, 2.2, 2.3, 5.4</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>g17</t>
+          <t>g16</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>g17</t>
+          <t>g10</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Which social norms help, and which harm</t>
+          <t>Spot &amp; remix gender stereotypes in media</t>
         </is>
       </c>
       <c r="N24" s="31" t="inlineStr">
@@ -2271,12 +2271,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>g19</t>
+          <t>g18</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Speak Up</t>
+          <t>Norm Storm</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2309,22 +2309,22 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>3.3, 5.5</t>
+          <t>3.2, 2.3</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>g18</t>
+          <t>g17</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>g11</t>
+          <t>g17</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Forms of gender-based harm &amp; where to get help</t>
+          <t>Which social norms help, and which harm</t>
         </is>
       </c>
       <c r="N25" s="31" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>g20</t>
+          <t>g19</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Defenders of the Body</t>
+          <t>Speak Up</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2360,180 +2360,180 @@
       <c r="F26" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>3.3, 5.5</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>g18</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>g11</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Forms of gender-based harm &amp; where to get help</t>
+        </is>
+      </c>
+      <c r="N26" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>g20</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Defenders of the Body</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Ch.3 · Ages 9–12</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>#059669</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>8.2, 8.3</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>g19</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>g12</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>HIV &amp; infections; reducing stigma</t>
         </is>
       </c>
-      <c r="N26" s="31" t="inlineStr">
+      <c r="N27" s="31" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>c3</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Capstone: Growing Up Smart</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Ch.3 · Ages 9–12</t>
         </is>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F28" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>g20</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L28" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M27" s="13" t="inlineStr">
+      <c r="M28" s="13" t="inlineStr">
         <is>
           <t>Chapter 3 graduation</t>
         </is>
       </c>
-      <c r="N27" s="32" t="inlineStr">
+      <c r="N28" s="32" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>g21</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Body Confident</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Ch.4 · Ages 12–15</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Body &amp; Growing Up</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>#0EA5E9</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>6.1, 6.3, 6.4</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>c3</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>g13</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Puberty depth &amp; body image</t>
-        </is>
-      </c>
-      <c r="N28" s="31" t="inlineStr">
-        <is>
-          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>g39</t>
+          <t>g21</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Bounce</t>
+          <t>Body Confident</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -2564,39 +2564,39 @@
       <c r="F29" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Feelings &amp; Life Skills</t>
+          <t>Body &amp; Growing Up</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>#F59E0B</t>
+          <t>#0EA5E9</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>5.6, 5.5</t>
+          <t>6.1, 6.3, 6.4</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>g21</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>g38</t>
+          <t>g13</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Resilience, stress &amp; mental health; supporting friends</t>
+          <t>Puberty depth &amp; body image</t>
         </is>
       </c>
       <c r="N29" s="31" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>g22</t>
+          <t>g39</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Plan It</t>
+          <t>Bounce</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2632,44 +2632,44 @@
       <c r="F30" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Sexual &amp; Reproductive Health</t>
+          <t>Feelings &amp; Life Skills</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>#059669</t>
+          <t>#F59E0B</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>6.2, 8.1</t>
+          <t>5.6, 5.5</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>g39</t>
+          <t>g21</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>g14</t>
+          <t>g38</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Fertility, pregnancy &amp; contraception</t>
-        </is>
-      </c>
-      <c r="N30" s="33" t="inlineStr">
-        <is>
-          <t>Gated</t>
+          <t>Resilience, stress &amp; mental health; supporting friends</t>
+        </is>
+      </c>
+      <c r="N30" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Outbreak: Stop the Spread</t>
+          <t>Plan It</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2717,22 +2717,22 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>6.2, 8.1</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>g22</t>
+          <t>g39</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>g20</t>
+          <t>g14</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>STIs &amp; HIV</t>
+          <t>Fertility, pregnancy &amp; contraception</t>
         </is>
       </c>
       <c r="N31" s="33" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Green Light / Red Light</t>
+          <t>Outbreak: Stop the Spread</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2768,39 +2768,39 @@
       <c r="F32" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>1.2, 4.2, 5.3, 7.1, 7.2</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g20</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Reading healthy vs unhealthy relationships (flagship)</t>
+          <t>STIs &amp; HIV</t>
         </is>
       </c>
       <c r="N32" s="33" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>g25</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>MythBuster: Gender</t>
+          <t>Green Light / Red Light</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2836,44 +2836,44 @@
       <c r="F33" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>3.1, 3.2</t>
+          <t>1.2, 4.2, 5.3, 7.1, 7.2</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>g18</t>
+          <t>g15</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Bust the gender myths teens hear constantly</t>
-        </is>
-      </c>
-      <c r="N33" s="31" t="inlineStr">
-        <is>
-          <t>Core</t>
+          <t>Reading healthy vs unhealthy relationships (flagship)</t>
+        </is>
+      </c>
+      <c r="N33" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g25</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Equalize</t>
+          <t>MythBuster: Gender</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>3.1, 3.2, 1.4, 2.2, 3.3, 4.1</t>
+          <t>3.1, 3.2</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>g25</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>g10</t>
+          <t>g18</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Equality pays off; child marriage</t>
+          <t>Bust the gender myths teens hear constantly</t>
         </is>
       </c>
       <c r="N34" s="31" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g26</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Stand Up</t>
+          <t>Equalize</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2972,39 +2972,39 @@
       <c r="F35" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>3.3, 4.1, 2.2</t>
+          <t>3.1, 3.2, 1.4, 2.2, 3.3, 4.1</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g25</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>g19</t>
+          <t>g10</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>GBV: bystander action &amp; rights</t>
+          <t>Equality pays off; child marriage</t>
         </is>
       </c>
       <c r="N35" s="31" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>g40</t>
+          <t>g27</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>Stand Up</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3057,27 +3057,27 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>4.3, 4.1, 5.5</t>
+          <t>3.3, 4.1, 2.2</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g26</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>g15</t>
+          <t>g19</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Teen online safety: grooming, sexting, sextortion &amp; footprint</t>
-        </is>
-      </c>
-      <c r="N36" s="33" t="inlineStr">
-        <is>
-          <t>Gated</t>
+          <t>GBV: bystander action &amp; rights</t>
+        </is>
+      </c>
+      <c r="N36" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>g28</t>
+          <t>g40</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Reality Check</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3108,180 +3108,180 @@
       <c r="F37" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Safety, Consent &amp; Boundaries</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>#DC2626</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>4.3, 4.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>g27</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>g15</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Teen online safety: grooming, sexting, sextortion &amp; footprint</t>
+        </is>
+      </c>
+      <c r="N37" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>g28</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Reality Check</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Ch.4 · Ages 12–15</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>5.1, 5.2, 5.4, 4.3, 5.5, 2.1, 2.3</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>g40</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>g16</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Decisions, media &amp; pornography literacy, finding help</t>
         </is>
       </c>
-      <c r="N37" s="33" t="inlineStr">
+      <c r="N38" s="33" t="inlineStr">
         <is>
           <t>Gated</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>c4</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Capstone: Reading Relationships</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Ch.4 · Ages 12–15</t>
         </is>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F39" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="I39" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="L39" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M38" s="13" t="inlineStr">
+      <c r="M39" s="13" t="inlineStr">
         <is>
           <t>Chapter 4 graduation</t>
         </is>
       </c>
-      <c r="N38" s="32" t="inlineStr">
+      <c r="N39" s="32" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>g29</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>My Choices, My Future</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Ch.5 · Ages 15–18</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Sexual &amp; Reproductive Health</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>#059669</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>c4</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>g22</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>Contraception, family planning &amp; services</t>
-        </is>
-      </c>
-      <c r="N39" s="33" t="inlineStr">
-        <is>
-          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3291,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Status: Know It</t>
+          <t>My Choices, My Future</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3329,22 +3329,22 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>g29</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>STI/HIV testing &amp; treatment</t>
+          <t>Contraception, family planning &amp; services</t>
         </is>
       </c>
       <c r="N40" s="33" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Mutual</t>
+          <t>Status: Know It</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3380,44 +3380,44 @@
       <c r="F41" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Sexual consent, legal age &amp; relationships</t>
-        </is>
-      </c>
-      <c r="N41" s="34" t="inlineStr">
-        <is>
-          <t>Sensitive ⚑</t>
+          <t>STI/HIV testing &amp; treatment</t>
+        </is>
+      </c>
+      <c r="N41" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Spectrum</t>
+          <t>Mutual</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3448,29 +3448,29 @@
       <c r="F42" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>7.1, 1.3, 3.1</t>
+          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Identity, orientation &amp; respect</t>
+          <t>Sexual consent, legal age &amp; relationships</t>
         </is>
       </c>
       <c r="N42" s="34" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Lead the Way</t>
+          <t>Spectrum</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3516,44 +3516,44 @@
       <c r="F43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>7.1, 1.3, 3.1</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Structural equality: pay gap, leadership, unpaid care</t>
-        </is>
-      </c>
-      <c r="N43" s="31" t="inlineStr">
-        <is>
-          <t>Core</t>
+          <t>Identity, orientation &amp; respect</t>
+        </is>
+      </c>
+      <c r="N43" s="34" t="inlineStr">
+        <is>
+          <t>Sensitive ⚑</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Change Makers</t>
+          <t>Lead the Way</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Campaign vs GBV &amp; inequality; the law</t>
+          <t>Structural equality: pay gap, leadership, unpaid care</t>
         </is>
       </c>
       <c r="N44" s="31" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>g35</t>
+          <t>g34</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Justice League: Rights Edition</t>
+          <t>Change Makers</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3652,39 +3652,39 @@
       <c r="F45" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Values, Rights &amp; Media</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>#475569</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g26</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Rights &amp; redress pathways</t>
+          <t>Campaign vs GBV &amp; inequality; the law</t>
         </is>
       </c>
       <c r="N45" s="31" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>g36</t>
+          <t>g35</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Decoded</t>
+          <t>Justice League: Rights Edition</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3737,93 +3737,229 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
+          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>g34</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>g27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Rights &amp; redress pathways</t>
+        </is>
+      </c>
+      <c r="N46" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>g42</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Life Ready</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>5.2, 5.6, 5.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>g35</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>g39</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Adult life-skills: self-knowledge, decisions, transitions &amp; support</t>
+        </is>
+      </c>
+      <c r="N47" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>g36</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Decoded</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Values, Rights &amp; Media</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>#475569</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
           <t>5.4, 4.3, 5.1, 5.6, 2.1, 2.3, 1.1</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>g35</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>g42</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr">
         <is>
           <t>Pornography &amp; critical thinking online</t>
         </is>
       </c>
-      <c r="N46" s="33" t="inlineStr">
+      <c r="N48" s="33" t="inlineStr">
         <is>
           <t>Gated</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>c5</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>Capstone: Ready for the World</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Ch.5 · Ages 15–18</t>
         </is>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F49" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I49" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>g36</t>
         </is>
       </c>
-      <c r="L47" s="11" t="inlineStr">
+      <c r="L49" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M47" s="13" t="inlineStr">
+      <c r="M49" s="13" t="inlineStr">
         <is>
           <t>Final graduation — look back at the whole world built since age 4</t>
         </is>
       </c>
-      <c r="N47" s="32" t="inlineStr">
+      <c r="N49" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3843,7 +3979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4188,6 +4324,20 @@
       <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Added g40 Firewall (teen online safety: grooming/sexting/sextortion/footprint, Ch.4, Thread B, topic 4.3) to close the 12–15 online-safety gap; re-tagged g28 Reality Check with 4.3 (image-abuse/reporting it already covers). Now 40 games + 5 capstones = 45 nodes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>Update — June 2026 (Thread C strengthened)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>Added g41 Heart Smart (feelings/empathy/getting-along, Ch.2) and g42 Life Ready (adult life-skills, Ch.5) so Feelings &amp; Life Skills (Thread C) now spans all 5 chapters. Now 42 games + 5 capstones = 47 nodes. Both feed the shared Life-Skills Toolkit spine.</t>
         </is>
       </c>
     </row>

--- a/scripts/master-node-table.xlsx
+++ b/scripts/master-node-table.xlsx
@@ -671,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SwipeEd — Master Node Table  (drop-in path spec: 42 games + 5 capstones, in order)</t>
+          <t>SwipeEd — Master Node Table  (drop-in path spec: 43 games + 5 capstones, in order)</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>g28</t>
+          <t>g43</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Reality Check</t>
+          <t>The Rabbit Hole</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3178,178 +3178,178 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
+          <t>E/G</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Media</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>#475569</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>3.2, 3.1, 5.4, 5.1, 1.3</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>g40</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>g25</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Online misogyny &amp; the manosphere: the funnel, the grift &amp; positive masculinity</t>
+        </is>
+      </c>
+      <c r="N38" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>g28</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Reality Check</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Ch.4 · Ages 12–15</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>5.1, 5.2, 5.4, 4.3, 5.5, 2.1, 2.3</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>g40</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>g43</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>g16</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Decisions, media &amp; pornography literacy, finding help</t>
         </is>
       </c>
-      <c r="N38" s="33" t="inlineStr">
+      <c r="N39" s="33" t="inlineStr">
         <is>
           <t>Gated</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>c4</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Capstone: Reading Relationships</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Ch.4 · Ages 12–15</t>
         </is>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F40" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="L40" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M39" s="13" t="inlineStr">
+      <c r="M40" s="13" t="inlineStr">
         <is>
           <t>Chapter 4 graduation</t>
         </is>
       </c>
-      <c r="N39" s="32" t="inlineStr">
+      <c r="N40" s="32" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>g29</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>My Choices, My Future</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Ch.5 · Ages 15–18</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Sexual &amp; Reproductive Health</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>#059669</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>c4</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>g22</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Contraception, family planning &amp; services</t>
-        </is>
-      </c>
-      <c r="N40" s="33" t="inlineStr">
-        <is>
-          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Status: Know It</t>
+          <t>My Choices, My Future</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>8.2, 8.3</t>
+          <t>8.1, 6.2, 6.1, 6.3, 5.5, 2.2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>g29</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>g23</t>
+          <t>g22</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>STI/HIV testing &amp; treatment</t>
+          <t>Contraception, family planning &amp; services</t>
         </is>
       </c>
       <c r="N41" s="33" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Mutual</t>
+          <t>Status: Know It</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3448,44 +3448,44 @@
       <c r="F42" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Safety, Consent &amp; Boundaries</t>
+          <t>Sexual &amp; Reproductive Health</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>#DC2626</t>
+          <t>#059669</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
+          <t>8.2, 8.3</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>g30</t>
+          <t>g29</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>g24</t>
+          <t>g23</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Sexual consent, legal age &amp; relationships</t>
-        </is>
-      </c>
-      <c r="N42" s="34" t="inlineStr">
-        <is>
-          <t>Sensitive ⚑</t>
+          <t>STI/HIV testing &amp; treatment</t>
+        </is>
+      </c>
+      <c r="N42" s="33" t="inlineStr">
+        <is>
+          <t>Gated</t>
         </is>
       </c>
     </row>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Spectrum</t>
+          <t>Mutual</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3516,29 +3516,29 @@
       <c r="F43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Relationships</t>
+          <t>Safety, Consent &amp; Boundaries</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>#EC4899</t>
+          <t>#DC2626</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>7.1, 1.3, 3.1</t>
+          <t>1.2, 4.2, 5.2, 5.3, 6.4, 7.2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>g31</t>
+          <t>g30</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Identity, orientation &amp; respect</t>
+          <t>Sexual consent, legal age &amp; relationships</t>
         </is>
       </c>
       <c r="N43" s="34" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Lead the Way</t>
+          <t>Spectrum</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3584,44 +3584,44 @@
       <c r="F44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Gender &amp; Respect</t>
+          <t>Relationships</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>#7C3AED</t>
+          <t>#EC4899</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>7.1, 1.3, 3.1</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>g32</t>
+          <t>g31</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>g26</t>
+          <t>g24</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Structural equality: pay gap, leadership, unpaid care</t>
-        </is>
-      </c>
-      <c r="N44" s="31" t="inlineStr">
-        <is>
-          <t>Core</t>
+          <t>Identity, orientation &amp; respect</t>
+        </is>
+      </c>
+      <c r="N44" s="34" t="inlineStr">
+        <is>
+          <t>Sensitive ⚑</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Change Makers</t>
+          <t>Lead the Way</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>g33</t>
+          <t>g32</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Campaign vs GBV &amp; inequality; the law</t>
+          <t>Structural equality: pay gap, leadership, unpaid care</t>
         </is>
       </c>
       <c r="N45" s="31" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>g35</t>
+          <t>g34</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Justice League: Rights Edition</t>
+          <t>Change Makers</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3720,39 +3720,39 @@
       <c r="F46" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Values, Rights &amp; Media</t>
+          <t>Gender &amp; Respect</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>#475569</t>
+          <t>#7C3AED</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
+          <t>3.2, 3.3, 4.1, 2.2, 1.4</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>g34</t>
+          <t>g33</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>g27</t>
+          <t>g26</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Rights &amp; redress pathways</t>
+          <t>Campaign vs GBV &amp; inequality; the law</t>
         </is>
       </c>
       <c r="N46" s="31" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>g42</t>
+          <t>g35</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Life Ready</t>
+          <t>Justice League: Rights Edition</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3788,39 +3788,39 @@
       <c r="F47" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Feelings &amp; Life Skills</t>
+          <t>Values, Rights &amp; Media</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>#F59E0B</t>
+          <t>#475569</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>5.2, 5.6, 5.1, 5.5</t>
+          <t>3.3, 2.2, 3.2, 4.1, 1.4</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>g35</t>
+          <t>g34</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>g39</t>
+          <t>g27</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Adult life-skills: self-knowledge, decisions, transitions &amp; support</t>
+          <t>Rights &amp; redress pathways</t>
         </is>
       </c>
       <c r="N47" s="31" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>g36</t>
+          <t>g42</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Decoded</t>
+          <t>Life Ready</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3856,110 +3856,178 @@
       <c r="F48" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>5.2, 5.6, 5.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>g35</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>g39</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Adult life-skills: self-knowledge, decisions, transitions &amp; support</t>
+        </is>
+      </c>
+      <c r="N48" s="31" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>g36</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Decoded</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Ch.5 · Ages 15–18</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Values, Rights &amp; Media</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>#475569</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>5.4, 4.3, 5.1, 5.6, 2.1, 2.3, 1.1</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>g42</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>g28</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Pornography &amp; critical thinking online</t>
         </is>
       </c>
-      <c r="N48" s="33" t="inlineStr">
+      <c r="N49" s="33" t="inlineStr">
         <is>
           <t>Gated</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>c5</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Capstone: Ready for the World</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>Capstone</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Ch.5 · Ages 15–18</t>
         </is>
       </c>
-      <c r="F49" s="11" t="n">
+      <c r="F50" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>Capstone milestone</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>#EAB308</t>
         </is>
       </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>g36</t>
         </is>
       </c>
-      <c r="L49" s="11" t="inlineStr">
+      <c r="L50" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M49" s="13" t="inlineStr">
+      <c r="M50" s="13" t="inlineStr">
         <is>
           <t>Final graduation — look back at the whole world built since age 4</t>
         </is>
       </c>
-      <c r="N49" s="32" t="inlineStr">
+      <c r="N50" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3979,7 +4047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4338,6 +4406,20 @@
       <c r="A34" s="36" t="inlineStr">
         <is>
           <t>Added g41 Heart Smart (feelings/empathy/getting-along, Ch.2) and g42 Life Ready (adult life-skills, Ch.5) so Feelings &amp; Life Skills (Thread C) now spans all 5 chapters. Now 42 games + 5 capstones = 47 nodes. Both feed the shared Life-Skills Toolkit spine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
+        <is>
+          <t>Update — June 2026 (manosphere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>Added g43 The Rabbit Hole (online misogyny &amp; the manosphere; Ch.4; dual thread E/G, node colour slate; topics 3.2/3.1/5.4/5.1/1.3; gating Gated) after g40 Firewall. Non-shaming, positive-masculinity-centred. Now 43 games + 5 capstones = 48 nodes.</t>
         </is>
       </c>
     </row>

--- a/scripts/master-node-table.xlsx
+++ b/scripts/master-node-table.xlsx
@@ -92,7 +92,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -169,6 +169,11 @@
         <fgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -306,6 +311,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -671,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -693,7 +701,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SwipeEd — Master Node Table  (drop-in path spec: 43 games + 5 capstones, in order)</t>
+          <t>SwipeEd — Master Node Table  (full lifelong path: kids' Ch.1–5 + adult Ch.6 College · Ch.7 Building a Life · Ch.8 Parenthood + Parent Layer)</t>
         </is>
       </c>
     </row>
@@ -4028,6 +4036,1978 @@
         </is>
       </c>
       <c r="N50" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>g44</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Consent, For Real</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Safety, Consent &amp; Boundaries</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>#DC2626</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>4.2, 4.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>c5</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>g31</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Adult consent in practice: alcohol, an ongoing yes, assault awareness &amp; survivor support</t>
+        </is>
+      </c>
+      <c r="N51" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>g45</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Swipe Right? — Dating &amp; Apps</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>#EC4899</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>1.2, 4.3, 5.5</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>g44</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>g24</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Modern dating &amp; app safety: meeting safely, ghosting, catfishing, digital boundaries</t>
+        </is>
+      </c>
+      <c r="N52" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>g46</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Real Relationships</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>#EC4899</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>1.2, 5.3, 4.1, 5.6</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>g45</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>g31</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Building healthy adult relationships; recognising &amp; leaving unhealthy ones; breakups</t>
+        </is>
+      </c>
+      <c r="N53" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>g47</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Own Your Health</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Sexual &amp; Reproductive Health</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>#059669</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>8.1, 8.2, 8.3, 7.2</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>g46</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>g30</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Adult SRH ownership: contraception, routine testing, sexual wellbeing &amp; pleasure, services</t>
+        </is>
+      </c>
+      <c r="N54" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>g48</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Money &amp; Independence</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>5.2, 2.2</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>g47</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>g42</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Work &amp; money: financial literacy &amp; independence; money in relationships</t>
+        </is>
+      </c>
+      <c r="N55" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>g49</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Mind &amp; Belonging</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>5.6, 5.5, 6.4</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>g48</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>g39</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>College mental health, loneliness &amp; leaving home; body image; help-seeking</t>
+        </is>
+      </c>
+      <c r="N56" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>g52</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Find Your Feet</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>5.6, 5.2, 5.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>g49</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>g42</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Career &amp; future anxiety: comparison, the pressure to have it ‘figured out’, purpose &amp; worth beyond your CV</t>
+        </is>
+      </c>
+      <c r="N57" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>g50</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Equal &amp; Confident</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>3.2, 3.1</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>g52</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>g33</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Gender equality at college/work; allyship; confidence, voice &amp; leadership</t>
+        </is>
+      </c>
+      <c r="N58" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>g51</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Know Your Rights (Adult)</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Values, Rights &amp; Media</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>#475569</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>2.2, 4.3, 3.3</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>g50</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>g35</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Adult rights: POSH/harassment, consent law, work/tenancy/cyber rights</t>
+        </is>
+      </c>
+      <c r="N59" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>c6</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Capstone: Standing on My Own</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Capstone</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>Ch.6 · Ages 18–22</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>Capstone milestone</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>#EAB308</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>g51</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M60" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 6 graduation — an independent young adult</t>
+        </is>
+      </c>
+      <c r="N60" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>g53</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Choosing &amp; Building</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>#EC4899</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>1.2, 1.4, 5.3, 2.1</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>c6</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>g46</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>Choosing a partner &amp; what makes a healthy long-term partnership/marriage (love &amp; arranged); commitment &amp; communication</t>
+        </is>
+      </c>
+      <c r="N61" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>g54</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Your Path, Your Call</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Relationships · Gender</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>#EC4899</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>1.2, 3.2, 2.2, 5.2</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>g53</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>g50</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>The freedom not to marry or have children; resisting the ‘settle down’ / ‘still-unmarried’ pressure (esp. on women); worth beyond marital status &amp; looks</t>
+        </is>
+      </c>
+      <c r="N62" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>g55</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Equal Partners</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>3.2, 1.1, 5.3</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>g54</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>g26</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>The equal home: sharing the domestic &amp; care load (the second shift), dual careers, equality in the relationship</t>
+        </is>
+      </c>
+      <c r="N63" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>g56</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Respect at Home</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Safety, Consent &amp; Boundaries</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>#DC2626</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>4.2, 4.1, 5.5</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>g55</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>g31</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>Consent &amp; mutual respect in marriage; recognising &amp; responding to coercion/DV; where to get help</t>
+        </is>
+      </c>
+      <c r="N64" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>g57</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>The Family Map</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>#EC4899</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>1.1, 2.3, 5.3</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>g56</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>g03</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>In-laws &amp; extended/joint family: navigating dynamics, setting boundaries, finding your place</t>
+        </is>
+      </c>
+      <c r="N65" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>g58</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Money, Together</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>5.2, 2.2</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>g57</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>g48</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Work &amp; money: joint finances &amp; planning; financial independence within a partnership; financial control as abuse</t>
+        </is>
+      </c>
+      <c r="N66" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>g59</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>If, When &amp; Whether</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Sexual &amp; Reproductive Health</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>#059669</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>8.1, 6.2, 6.3</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>g58</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>g29</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>Reproductive planning: whether, when &amp; spacing children; fertility awareness; preconception health; infertility &amp; options</t>
+        </is>
+      </c>
+      <c r="N67" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>g60</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Many Ways to Family</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>F/D</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>SRH · Relationships</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>#059669</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>8.1, 1.1, 2.2</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>g59</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>g32</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>Diverse routes to family — adoption/fostering, surrogacy &amp; IVF, single &amp; LGBTQ+ parenthood — and the gendered barriers (e.g. single men &amp; girl-child adoption, CARA 2022)</t>
+        </is>
+      </c>
+      <c r="N68" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>c7</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Capstone: Building Together</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Capstone</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>Ch.7 · 22 → first child</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>Capstone milestone</t>
+        </is>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>#EAB308</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>g60</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 7 graduation — a life built together, or on your own terms</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>g61</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Us, After Kids</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>#EC4899</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>1.2, 5.3, 7.1</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>c7</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>g53</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Keeping the partnership &amp; intimacy alive with kids in the picture; co-parenting connection &amp; communication under load</t>
+        </is>
+      </c>
+      <c r="N70" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>g62</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Equal Parents</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Gender &amp; Respect</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>3.2, 1.4, 1.1</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>g61</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>g55</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Co-parenting as equals — sharing the care &amp; mental load, involved fatherhood, breaking gendered parenting</t>
+        </is>
+      </c>
+      <c r="N71" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>g63</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Looking After You</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Feelings &amp; Life Skills</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>5.6, 5.5</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>g62</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>g49</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Parental wellbeing &amp; mental health; burnout; your own needs matter; the Life-Skills Toolkit under load</t>
+        </is>
+      </c>
+      <c r="N72" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>g64</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>The Talks (Age by Age)</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Parent Layer · RSE guidance</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>#059669</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>4.2, 6.3, 7.1, 2.1</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>g63</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>g02</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>PARENT LAYER — age-by-age RSE guidance mapped to your child's journey (bodies, consent, puberty, relationships, sexuality, online); many small talks; facts + your values</t>
+        </is>
+      </c>
+      <c r="N73" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>g65</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Break the Cycle</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Parent Layer · Positive Parenting</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>5.6, 5.3</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>g64</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>g38</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Positive parenting &amp; breaking generational trauma; discipline without fear, shame or hitting; repair; healing your own wounds (Unlearn→Relearn, for parents)</t>
+        </is>
+      </c>
+      <c r="N74" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>g66</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Raising Gender-Diverse Kids</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Parent Layer · Positive Parenting</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>#7C3AED</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>3.1, 1.3, 7.1</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>g65</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>g32</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>Affirming &amp; protecting an LGBTQ+ or gender-nonconforming child; not forcing norms; being their safe place</t>
+        </is>
+      </c>
+      <c r="N75" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>g67</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Raising Neurodiverse Kids</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Parent Layer · Positive Parenting</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>#F59E0B</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>5.6, 1.3, 5.5</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>g66</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>g04</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Understanding &amp; supporting autism, ADHD &amp; learning differences; accommodating, advocating, de-stigmatising</t>
+        </is>
+      </c>
+      <c r="N76" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>g68</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Navigating Addictions</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Parent Layer · Positive Parenting</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>#DC2626</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>5.1, 5.5, 5.6</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>g67</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>g39</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>Recognising &amp; responding (without shame) to a child's substance / screen / gaming dependence; getting help early; modelling healthy habits</t>
+        </is>
+      </c>
+      <c r="N77" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>g69</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Be the Safe Adult</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Parent Layer · Safeguarding</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>#DC2626</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>4.1, 4.2, 4.3, 5.5</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>g68</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>g08</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>Safeguarding literacy: spotting abuse, POCSO basics, online dangers, and how to respond to a disclosure — the trusted adult the kids' journey assumes</t>
+        </is>
+      </c>
+      <c r="N78" s="39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>c8</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Capstone: Raising the Next Generation</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Capstone</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>Ch.8 · Parenthood (first child on)</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>Capstone milestone</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>#EAB308</t>
+        </is>
+      </c>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>g69</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="13" t="inlineStr">
+        <is>
+          <t>Final graduation — guiding the next generation; the loop comes full circle</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4047,7 +6027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4420,6 +6400,48 @@
       <c r="A37" s="36" t="inlineStr">
         <is>
           <t>Added g43 The Rabbit Hole (online misogyny &amp; the manosphere; Ch.4; dual thread E/G, node colour slate; topics 3.2/3.1/5.4/5.1/1.3; gating Gated) after g40 Firewall. Non-shaming, positive-masculinity-centred. Now 43 games + 5 capstones = 48 nodes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>Adult journey — Ch.6 College added (June 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>Adult chapters continue the same product &amp; linear chain. Ch.6 College (18–22): g44–g52 + c6. gating ‘Open’ = adult, comprehensive, not school-comfort-gated. Chapters 7 (Building a Life) &amp; 8 (Parenthood + Parent Layer) to follow, one layer at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
+          <t>Adult journey — Ch.7 Building a Life added (June 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>Ch.7 (22 → first child): g53–g60 + c7. Includes the diverse-paths content — freedom not to marry/childfree &amp; the ‘still-unmarried’ stigma (g54), and diverse routes to family incl. the single-man / girl-child adoption barrier (g60). Ch.8 Parenthood + the Parent Layer to follow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="38" t="inlineStr">
+        <is>
+          <t>Adult journey — Ch.8 Parenthood + Parent Layer added (June 2026); adult node-map complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="36" t="inlineStr">
+        <is>
+          <t>Ch.8 (first child on): g61–g63 = the parent's own continuing journey; g64–g69 = the PARENT LAYER (‘SwipeEd Raising’) — age-by-age RSE guidance (g64) + positive parenting: break the cycle/generational trauma (g65), raising gender-diverse (g66) &amp; neurodiverse (g67) kids, navigating addictions (g68), being the safe adult (g69). c8 closes the generational loop. The full lifelong journey (Ch.1–8) is now mapped.</t>
         </is>
       </c>
     </row>
